--- a/data/human/adult/validation/Scenarios/DrugsValidation.xlsx
+++ b/data/human/adult/validation/Scenarios/DrugsValidation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\stress_update\source\data\human\adult\validation\Scenarios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\release_updates\source\data\human\adult\validation\Scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3818FEB7-04CE-4FCC-85A1-8EF8DE3FBCF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{074E03F0-4DE1-453D-9FAA-37FC0DAD93FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1590" yWindow="6990" windowWidth="37740" windowHeight="21480" tabRatio="736" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28770" yWindow="8250" windowWidth="24735" windowHeight="19980" tabRatio="736" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="18" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="Furosemide" sheetId="25" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Summary!$B$1:$N$17</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Summary!$B$1:$N$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="188">
   <si>
     <t>Event</t>
   </si>
@@ -541,9 +541,6 @@
     <t>[-10, -13]  @cite martinsson1986analysis</t>
   </si>
   <si>
-    <t>|&lt;span class="warning"&gt;</t>
-  </si>
-  <si>
     <t>[46, 66] NC to neglible @cite ensinger1992relationship</t>
   </si>
   <si>
@@ -599,6 +596,18 @@
   </si>
   <si>
     <t xml:space="preserve">0-25% Decrease @cite chase2010model </t>
+  </si>
+  <si>
+    <t>Computed Systolic Blood Pressure Change (mmHg)</t>
+  </si>
+  <si>
+    <t>Computed Diastolic Blood Pressure Change (mmHg)</t>
+  </si>
+  <si>
+    <t>Furosemide</t>
+  </si>
+  <si>
+    <t>Administer 40 mg injection of Furosemide</t>
   </si>
 </sst>
 </file>
@@ -1195,7 +1204,7 @@
       <alignment wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1220,9 +1229,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1700,7 +1706,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.85546875" bestFit="1" customWidth="1"/>
@@ -1718,13 +1724,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>52</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="40" t="s">
         <v>52</v>
       </c>
       <c r="D1" s="6" t="s">
@@ -1733,583 +1739,688 @@
       <c r="E1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="G1" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="H1" s="38" t="s">
+      <c r="G1" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="I1" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="J1" s="37" t="s">
+      <c r="I1" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="K1" s="43" t="s">
+      <c r="K1" s="42" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="E2" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="F2" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="G2" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="H2" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="I2" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="J2" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="K2" s="40" t="s">
+      <c r="A2" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="K2" s="39" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="39" t="s">
         <v>52</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="39" t="s">
         <v>52</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E3" s="44" t="s">
+      <c r="E3" s="43" t="s">
         <v>54</v>
       </c>
       <c r="F3" s="9">
-        <v>5</v>
-      </c>
-      <c r="G3" s="52" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="51" t="s">
         <v>94</v>
       </c>
       <c r="H3" s="7">
         <v>0</v>
       </c>
-      <c r="I3" s="52" t="s">
+      <c r="I3" s="51" t="s">
         <v>95</v>
       </c>
       <c r="J3" s="8">
-        <v>0</v>
-      </c>
-      <c r="K3" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="41" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="39" t="s">
         <v>52</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C4" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C4" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="E4" s="44" t="s">
+      <c r="E4" s="43" t="s">
         <v>54</v>
       </c>
       <c r="F4" s="9">
         <v>5</v>
       </c>
-      <c r="G4" s="52" t="s">
+      <c r="G4" s="51" t="s">
         <v>94</v>
       </c>
       <c r="H4" s="7">
         <v>0</v>
       </c>
-      <c r="I4" s="52" t="s">
+      <c r="I4" s="51" t="s">
         <v>95</v>
       </c>
       <c r="J4" s="8">
         <v>0</v>
       </c>
-      <c r="K4" s="42" t="s">
+      <c r="K4" s="41" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="39" t="s">
         <v>52</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="C5" s="39" t="s">
         <v>52</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="43" t="s">
         <v>54</v>
       </c>
       <c r="F5" s="9">
         <v>5</v>
       </c>
-      <c r="G5" s="52" t="s">
+      <c r="G5" s="51" t="s">
         <v>94</v>
       </c>
       <c r="H5" s="7">
         <v>0</v>
       </c>
-      <c r="I5" s="52" t="s">
+      <c r="I5" s="51" t="s">
         <v>95</v>
       </c>
       <c r="J5" s="8">
         <v>0</v>
       </c>
-      <c r="K5" s="42" t="s">
+      <c r="K5" s="41" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="40" t="s">
+      <c r="A6" s="39" t="s">
         <v>52</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="39" t="s">
         <v>52</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="44" t="s">
+      <c r="E6" s="43" t="s">
         <v>54</v>
       </c>
       <c r="F6" s="9">
         <v>5</v>
       </c>
-      <c r="G6" s="52" t="s">
+      <c r="G6" s="51" t="s">
         <v>94</v>
       </c>
       <c r="H6" s="7">
         <v>0</v>
       </c>
-      <c r="I6" s="52" t="s">
+      <c r="I6" s="51" t="s">
         <v>95</v>
       </c>
       <c r="J6" s="8">
         <v>0</v>
       </c>
-      <c r="K6" s="42" t="s">
+      <c r="K6" s="41" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="39" t="s">
         <v>52</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="40" t="s">
+        <v>186</v>
+      </c>
+      <c r="C7" s="39" t="s">
         <v>52</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="44" t="s">
+        <v>187</v>
+      </c>
+      <c r="E7" s="43" t="s">
         <v>54</v>
       </c>
       <c r="F7" s="9">
-        <v>5</v>
-      </c>
-      <c r="G7" s="52" t="s">
+        <v>4</v>
+      </c>
+      <c r="G7" s="51" t="s">
         <v>94</v>
       </c>
       <c r="H7" s="7">
         <v>0</v>
       </c>
-      <c r="I7" s="52" t="s">
+      <c r="I7" s="51" t="s">
         <v>95</v>
       </c>
       <c r="J7" s="8">
         <v>0</v>
       </c>
-      <c r="K7" s="42" t="s">
+      <c r="K7" s="41" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="40" t="s">
+      <c r="A8" s="39" t="s">
         <v>52</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C8" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="39" t="s">
         <v>52</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="E8" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="43" t="s">
         <v>54</v>
       </c>
       <c r="F8" s="9">
         <v>5</v>
       </c>
-      <c r="G8" s="52" t="s">
+      <c r="G8" s="51" t="s">
         <v>94</v>
       </c>
       <c r="H8" s="7">
         <v>0</v>
       </c>
-      <c r="I8" s="52" t="s">
+      <c r="I8" s="51" t="s">
         <v>95</v>
       </c>
       <c r="J8" s="8">
         <v>0</v>
       </c>
-      <c r="K8" s="42" t="s">
+      <c r="K8" s="41" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="40" t="s">
+      <c r="A9" s="39" t="s">
         <v>52</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="40" t="s">
+        <v>172</v>
+      </c>
+      <c r="C9" s="39" t="s">
         <v>52</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="44" t="s">
+        <v>173</v>
+      </c>
+      <c r="E9" s="43" t="s">
         <v>54</v>
       </c>
       <c r="F9" s="9">
         <v>5</v>
       </c>
-      <c r="G9" s="52" t="s">
+      <c r="G9" s="51" t="s">
         <v>94</v>
       </c>
       <c r="H9" s="7">
         <v>0</v>
       </c>
-      <c r="I9" s="52" t="s">
+      <c r="I9" s="51" t="s">
         <v>95</v>
       </c>
       <c r="J9" s="8">
         <v>0</v>
       </c>
-      <c r="K9" s="42" t="s">
+      <c r="K9" s="41" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="44" t="s">
+      <c r="A10" s="39" t="s">
         <v>52</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="39" t="s">
         <v>52</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="43" t="s">
         <v>54</v>
       </c>
       <c r="F10" s="9">
         <v>5</v>
       </c>
-      <c r="G10" s="52" t="s">
+      <c r="G10" s="51" t="s">
         <v>94</v>
       </c>
       <c r="H10" s="7">
         <v>0</v>
       </c>
-      <c r="I10" s="52" t="s">
+      <c r="I10" s="51" t="s">
         <v>95</v>
       </c>
       <c r="J10" s="8">
         <v>0</v>
       </c>
-      <c r="K10" s="42" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="40" t="s">
+      <c r="K10" s="41" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="43" t="s">
         <v>52</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E11" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="43" t="s">
         <v>54</v>
       </c>
       <c r="F11" s="9">
         <v>5</v>
       </c>
-      <c r="G11" s="52" t="s">
+      <c r="G11" s="51" t="s">
         <v>94</v>
       </c>
       <c r="H11" s="7">
         <v>0</v>
       </c>
-      <c r="I11" s="52" t="s">
+      <c r="I11" s="51" t="s">
         <v>95</v>
       </c>
       <c r="J11" s="8">
         <v>0</v>
       </c>
-      <c r="K11" s="42" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="40" t="s">
+      <c r="K11" s="41" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="39" t="s">
         <v>52</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="39" t="s">
         <v>52</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="E12" s="44" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="43" t="s">
         <v>54</v>
       </c>
       <c r="F12" s="9">
         <v>5</v>
       </c>
-      <c r="G12" s="52" t="s">
+      <c r="G12" s="51" t="s">
         <v>94</v>
       </c>
       <c r="H12" s="7">
         <v>0</v>
       </c>
-      <c r="I12" s="52" t="s">
+      <c r="I12" s="51" t="s">
         <v>95</v>
       </c>
       <c r="J12" s="8">
         <v>0</v>
       </c>
-      <c r="K12" s="42" t="s">
+      <c r="K12" s="41" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="40" t="s">
+      <c r="A13" s="39" t="s">
         <v>52</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="39" t="s">
         <v>52</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="44" t="s">
+        <v>112</v>
+      </c>
+      <c r="E13" s="43" t="s">
         <v>54</v>
       </c>
       <c r="F13" s="9">
         <v>5</v>
       </c>
-      <c r="G13" s="52" t="s">
+      <c r="G13" s="51" t="s">
         <v>94</v>
       </c>
       <c r="H13" s="7">
         <v>0</v>
       </c>
-      <c r="I13" s="52" t="s">
+      <c r="I13" s="51" t="s">
         <v>95</v>
       </c>
       <c r="J13" s="8">
         <v>0</v>
       </c>
-      <c r="K13" s="42" t="s">
+      <c r="K13" s="41" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="40" t="s">
+      <c r="A14" s="39" t="s">
         <v>52</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="43" t="s">
         <v>54</v>
       </c>
       <c r="F14" s="9">
         <v>5</v>
       </c>
-      <c r="G14" s="52" t="s">
+      <c r="G14" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="H14" s="15">
+      <c r="H14" s="7">
         <v>0</v>
       </c>
-      <c r="I14" s="52" t="s">
+      <c r="I14" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="8">
         <v>0</v>
       </c>
-      <c r="K14" s="42" t="s">
+      <c r="K14" s="41" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="40" t="s">
+      <c r="A15" s="39" t="s">
         <v>52</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" s="9">
+        <v>5</v>
+      </c>
+      <c r="G15" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="H15" s="14">
+        <v>0</v>
+      </c>
+      <c r="I15" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="J15" s="15">
+        <v>0</v>
+      </c>
+      <c r="K15" s="41" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="5" t="s">
+      <c r="C16" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="44" t="s">
-        <v>54</v>
-      </c>
-      <c r="F15" s="9">
+      <c r="E16" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" s="9">
         <v>2</v>
       </c>
-      <c r="G15" s="52" t="s">
-        <v>94</v>
-      </c>
-      <c r="H15" s="7">
-        <v>0</v>
-      </c>
-      <c r="I15" s="52" t="s">
-        <v>95</v>
-      </c>
-      <c r="J15" s="8">
-        <v>3</v>
-      </c>
-      <c r="K15" s="42" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="44" t="s">
-        <v>54</v>
-      </c>
-      <c r="F16" s="9">
-        <v>5</v>
-      </c>
-      <c r="G16" s="52" t="s">
+      <c r="G16" s="51" t="s">
         <v>94</v>
       </c>
       <c r="H16" s="7">
         <v>0</v>
       </c>
-      <c r="I16" s="52" t="s">
+      <c r="I16" s="51" t="s">
         <v>95</v>
       </c>
       <c r="J16" s="8">
+        <v>3</v>
+      </c>
+      <c r="K16" s="41" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="9">
+        <v>5</v>
+      </c>
+      <c r="G17" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="H17" s="7">
         <v>0</v>
       </c>
-      <c r="K16" s="42" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" s="45"/>
-      <c r="C17" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" s="46" t="s">
+      <c r="I17" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="J17" s="8">
+        <v>0</v>
+      </c>
+      <c r="K17" s="41" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C18" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E18" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="9">
+        <v>20</v>
+      </c>
+      <c r="G18" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="H18" s="7">
+        <v>0</v>
+      </c>
+      <c r="I18" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="J18" s="8">
+        <v>0</v>
+      </c>
+      <c r="K18" s="41" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C19" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E19" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19" s="9">
+        <v>12</v>
+      </c>
+      <c r="G19" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="H19" s="7">
+        <v>2</v>
+      </c>
+      <c r="I19" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="J19" s="8">
+        <v>4</v>
+      </c>
+      <c r="K19" s="41" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="E17" s="45" t="s">
-        <v>54</v>
-      </c>
-      <c r="F17" s="47">
-        <f>SUM(F3:F16)</f>
-        <v>67</v>
-      </c>
-      <c r="G17" s="48" t="s">
+      <c r="E20" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="F20" s="46">
+        <f>SUM(F3:F19)</f>
+        <v>102</v>
+      </c>
+      <c r="G20" s="47" t="s">
         <v>94</v>
       </c>
-      <c r="H17" s="49">
-        <f>SUM(H3:H16)</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="48" t="s">
+      <c r="H20" s="48">
+        <f>SUM(H3:H19)</f>
+        <v>2</v>
+      </c>
+      <c r="I20" s="47" t="s">
         <v>95</v>
       </c>
-      <c r="J17" s="50">
-        <f>SUM(J3:J16)</f>
-        <v>3</v>
-      </c>
-      <c r="K17" s="51" t="s">
+      <c r="J20" s="49">
+        <f>SUM(J3:J19)</f>
+        <v>8</v>
+      </c>
+      <c r="K20" s="50" t="s">
         <v>56</v>
       </c>
     </row>
@@ -2335,57 +2446,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="29" t="s">
+      <c r="A1" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="28" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="29" t="s">
+      <c r="A2" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="28" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="B3" s="27" t="s">
+      <c r="A3" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="28" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="28" t="s">
         <v>56</v>
       </c>
     </row>
@@ -2402,274 +2513,274 @@
   <dimension ref="A2:W14"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1" style="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="1" style="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" style="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="1" style="21" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.42578125" style="21" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="1" style="21" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.5703125" style="21" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" style="21" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.28515625" style="21" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="27.28515625" style="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25.28515625" style="21" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.28515625" style="21" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="25.28515625" style="21" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="27.28515625" style="21" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.140625" style="21" customWidth="1"/>
-    <col min="17" max="17" width="27.28515625" style="21" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="24.28515625" style="21" customWidth="1"/>
-    <col min="19" max="19" width="27.28515625" style="21" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.5703125" style="21" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="27.28515625" style="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="18.5703125" style="21" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.140625" style="21" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="21"/>
+    <col min="1" max="1" width="1" style="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="1" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="1" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.42578125" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="1" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.28515625" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.28515625" style="20" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.28515625" style="20" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.28515625" style="20" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.28515625" style="20" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.28515625" style="20" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.140625" style="20" customWidth="1"/>
+    <col min="17" max="17" width="27.28515625" style="20" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.28515625" style="20" customWidth="1"/>
+    <col min="19" max="19" width="27.28515625" style="20" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.28515625" style="20" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="18.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="20"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:23" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" s="34" t="s">
+      <c r="A2" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="34" t="s">
+      <c r="C2" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="F2" s="26" t="s">
+      <c r="E2" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="H2" s="26" t="s">
+      <c r="G2" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H2" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="J2" s="25" t="s">
+      <c r="I2" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="J2" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="L2" s="17" t="s">
+      <c r="K2" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="L2" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="N2" s="17" t="s">
+      <c r="M2" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="N2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="O2" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="P2" s="17" t="s">
+      <c r="O2" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="P2" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="Q2" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="R2" s="17" t="s">
+      <c r="Q2" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="R2" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="S2" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="T2" s="17" t="s">
+      <c r="S2" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="T2" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="U2" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="V2" s="17" t="s">
+      <c r="U2" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="V2" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="W2" s="19" t="s">
+      <c r="W2" s="18" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A3" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="B3" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="F3" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="H3" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="I3" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="J3" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="K3" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="L3" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="M3" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="N3" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="O3" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="P3" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q3" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="R3" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="S3" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="T3" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="U3" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="V3" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="W3" s="19" t="s">
+      <c r="A3" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="J3" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="K3" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="L3" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="M3" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="N3" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="O3" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="P3" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q3" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="R3" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="S3" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="T3" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="U3" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="V3" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="W3" s="18" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="36" t="s">
+      <c r="A4" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="36" t="s">
+      <c r="C4" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="F4" s="36">
+      <c r="E4" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="35">
         <v>30</v>
       </c>
-      <c r="G4" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="H4" s="32">
+      <c r="G4" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H4" s="31">
         <v>200</v>
       </c>
-      <c r="I4" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="J4" s="23" t="s">
+      <c r="I4" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="J4" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="L4" s="53" t="s">
+      <c r="L4" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="M4" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="N4" s="23" t="s">
+      <c r="M4" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="N4" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="O4" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="P4" s="18" t="s">
+      <c r="O4" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="P4" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="Q4" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="R4" s="18" t="s">
+      <c r="Q4" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="R4" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="S4" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="T4" s="24" t="s">
+      <c r="S4" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="T4" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="U4" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="V4" s="18" t="s">
+      <c r="U4" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="V4" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="W4" s="35" t="s">
+      <c r="W4" s="34" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="P5" s="21" t="s">
+      <c r="P5" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="R5" s="21" t="s">
+      <c r="R5" s="20" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2693,7 +2804,7 @@
     <col min="5" max="5" width="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.5703125" style="54" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.5703125" style="53" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="29.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="36.7109375" customWidth="1"/>
     <col min="11" max="11" width="34.5703125" customWidth="1"/>
@@ -2770,55 +2881,55 @@
       <c r="A3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>53</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="21" t="s">
         <v>53</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="21" t="s">
         <v>53</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="21" t="s">
         <v>53</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="J3" s="22" t="s">
+      <c r="J3" s="21" t="s">
         <v>53</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="L3" s="22" t="s">
+      <c r="L3" s="21" t="s">
         <v>53</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="N3" s="22" t="s">
+      <c r="N3" s="21" t="s">
         <v>53</v>
       </c>
       <c r="O3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="P3" s="22" t="s">
+      <c r="P3" s="21" t="s">
         <v>53</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="R3" s="22" t="s">
+      <c r="R3" s="21" t="s">
         <v>53</v>
       </c>
       <c r="S3" s="5" t="s">
@@ -2853,31 +2964,31 @@
       <c r="I4" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="13" t="s">
         <v>71</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="L4" s="14" t="s">
+      <c r="L4" s="13" t="s">
         <v>65</v>
       </c>
       <c r="M4" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="N4" s="14" t="s">
-        <v>184</v>
+      <c r="N4" s="13" t="s">
+        <v>183</v>
       </c>
       <c r="O4" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="P4" s="12" t="s">
+      <c r="P4" s="11" t="s">
         <v>66</v>
       </c>
       <c r="Q4" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="R4" s="13" t="s">
+      <c r="R4" s="12" t="s">
         <v>97</v>
       </c>
       <c r="S4" s="5" t="s">
@@ -2912,31 +3023,31 @@
       <c r="I5" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="J5" s="13" t="s">
         <v>118</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="L5" s="14" t="s">
+      <c r="L5" s="13" t="s">
         <v>118</v>
       </c>
       <c r="M5" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="N5" s="14" t="s">
+      <c r="N5" s="13" t="s">
         <v>118</v>
       </c>
       <c r="O5" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="P5" s="12" t="s">
+      <c r="P5" s="11" t="s">
         <v>119</v>
       </c>
       <c r="Q5" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="R5" s="13" t="s">
+      <c r="R5" s="12" t="s">
         <v>117</v>
       </c>
       <c r="S5" s="5" t="s">
@@ -2971,31 +3082,31 @@
       <c r="I6" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="13" t="s">
         <v>76</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="L6" s="14" t="s">
+      <c r="L6" s="13" t="s">
         <v>76</v>
       </c>
       <c r="M6" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="N6" s="14" t="s">
+      <c r="N6" s="13" t="s">
         <v>76</v>
       </c>
       <c r="O6" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="P6" s="14" t="s">
+      <c r="P6" s="13" t="s">
         <v>85</v>
       </c>
       <c r="Q6" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="R6" s="13" t="s">
+      <c r="R6" s="12" t="s">
         <v>97</v>
       </c>
       <c r="S6" s="5" t="s">
@@ -3030,31 +3141,31 @@
       <c r="I7" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="J7" s="13" t="s">
         <v>77</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="L7" s="14" t="s">
+      <c r="L7" s="13" t="s">
         <v>77</v>
       </c>
       <c r="M7" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="N7" s="14" t="s">
+      <c r="N7" s="13" t="s">
         <v>77</v>
       </c>
       <c r="O7" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="P7" s="14" t="s">
+      <c r="P7" s="13" t="s">
         <v>86</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="R7" s="14" t="s">
+      <c r="R7" s="13" t="s">
         <v>97</v>
       </c>
       <c r="S7" s="5" t="s">
@@ -3066,13 +3177,13 @@
         <v>52</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>175</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>176</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>52</v>
@@ -3089,31 +3200,31 @@
       <c r="I8" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="J8" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="P8" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="K8" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="L8" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="N8" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="P8" s="14" t="s">
-        <v>178</v>
-      </c>
       <c r="Q8" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="R8" s="14" t="s">
+      <c r="R8" s="13" t="s">
         <v>117</v>
       </c>
       <c r="S8" s="5" t="s">
@@ -3148,31 +3259,31 @@
       <c r="I9" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="J9" s="13" t="s">
         <v>78</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="L9" s="14" t="s">
+      <c r="L9" s="13" t="s">
         <v>83</v>
       </c>
       <c r="M9" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="N9" s="14" t="s">
+      <c r="N9" s="13" t="s">
         <v>83</v>
       </c>
       <c r="O9" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="P9" s="14" t="s">
-        <v>179</v>
+      <c r="P9" s="13" t="s">
+        <v>178</v>
       </c>
       <c r="Q9" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="R9" s="12" t="s">
+      <c r="R9" s="11" t="s">
         <v>98</v>
       </c>
       <c r="S9" s="5" t="s">
@@ -3207,31 +3318,31 @@
       <c r="I10" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="J10" s="14" t="s">
+      <c r="J10" s="13" t="s">
         <v>79</v>
       </c>
       <c r="K10" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="L10" s="14" t="s">
+      <c r="L10" s="13" t="s">
         <v>114</v>
       </c>
       <c r="M10" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="N10" s="14" t="s">
+      <c r="N10" s="13" t="s">
         <v>114</v>
       </c>
       <c r="O10" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="P10" s="14" t="s">
+      <c r="P10" s="13" t="s">
         <v>87</v>
       </c>
       <c r="Q10" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="R10" s="12" t="s">
+      <c r="R10" s="11" t="s">
         <v>98</v>
       </c>
       <c r="S10" s="5" t="s">
@@ -3266,31 +3377,31 @@
       <c r="I11" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="J11" s="14" t="s">
+      <c r="J11" s="13" t="s">
         <v>76</v>
       </c>
       <c r="K11" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="L11" s="14" t="s">
+      <c r="L11" s="13" t="s">
         <v>76</v>
       </c>
       <c r="M11" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="N11" s="14" t="s">
+      <c r="N11" s="13" t="s">
         <v>84</v>
       </c>
       <c r="O11" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="P11" s="14" t="s">
+      <c r="P11" s="13" t="s">
         <v>85</v>
       </c>
       <c r="Q11" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="R11" s="13" t="s">
+      <c r="R11" s="12" t="s">
         <v>97</v>
       </c>
       <c r="S11" s="5" t="s">
@@ -3325,31 +3436,31 @@
       <c r="I12" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="J12" s="14" t="s">
+      <c r="J12" s="13" t="s">
         <v>80</v>
       </c>
       <c r="K12" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="L12" s="14" t="s">
+      <c r="L12" s="13" t="s">
         <v>80</v>
       </c>
       <c r="M12" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="N12" s="14" t="s">
+      <c r="N12" s="13" t="s">
         <v>80</v>
       </c>
       <c r="O12" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="P12" s="14" t="s">
+      <c r="P12" s="13" t="s">
         <v>88</v>
       </c>
       <c r="Q12" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="R12" s="14" t="s">
+      <c r="R12" s="13" t="s">
         <v>99</v>
       </c>
       <c r="S12" s="5" t="s">
@@ -3384,31 +3495,31 @@
       <c r="I13" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="J13" s="14" t="s">
+      <c r="J13" s="13" t="s">
         <v>67</v>
       </c>
       <c r="K13" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="L13" s="14" t="s">
+      <c r="L13" s="13" t="s">
         <v>68</v>
       </c>
       <c r="M13" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="N13" s="14" t="s">
+      <c r="N13" s="13" t="s">
         <v>68</v>
       </c>
       <c r="O13" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="P13" s="14" t="s">
+      <c r="P13" s="13" t="s">
         <v>69</v>
       </c>
       <c r="Q13" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="R13" s="14" t="s">
+      <c r="R13" s="13" t="s">
         <v>70</v>
       </c>
       <c r="S13" s="5" t="s">
@@ -3443,31 +3554,31 @@
       <c r="I14" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="J14" s="14" t="s">
+      <c r="J14" s="13" t="s">
         <v>70</v>
       </c>
       <c r="K14" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="L14" s="14" t="s">
+      <c r="L14" s="13" t="s">
         <v>70</v>
       </c>
       <c r="M14" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="N14" s="14" t="s">
+      <c r="N14" s="13" t="s">
         <v>70</v>
       </c>
       <c r="O14" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="P14" s="14" t="s">
+      <c r="P14" s="13" t="s">
         <v>70</v>
       </c>
       <c r="Q14" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="R14" s="14" t="s">
+      <c r="R14" s="13" t="s">
         <v>70</v>
       </c>
       <c r="S14" s="5" t="s">
@@ -3502,31 +3613,31 @@
       <c r="I15" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="J15" s="14" t="s">
+      <c r="J15" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="L15" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="K15" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="L15" s="14" t="s">
+      <c r="M15" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N15" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="M15" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="N15" s="14" t="s">
-        <v>183</v>
-      </c>
       <c r="O15" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="P15" s="14" t="s">
-        <v>180</v>
+      <c r="P15" s="13" t="s">
+        <v>179</v>
       </c>
       <c r="Q15" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="R15" s="12" t="s">
+      <c r="R15" s="11" t="s">
         <v>98</v>
       </c>
       <c r="S15" s="5" t="s">
@@ -3561,31 +3672,31 @@
       <c r="I16" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="J16" s="53" t="s">
+      <c r="J16" s="52" t="s">
         <v>81</v>
       </c>
       <c r="K16" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="L16" s="53" t="s">
+      <c r="L16" s="52" t="s">
         <v>81</v>
       </c>
       <c r="M16" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="N16" s="53" t="s">
+      <c r="N16" s="52" t="s">
         <v>81</v>
       </c>
       <c r="O16" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="P16" s="14" t="s">
+      <c r="P16" s="13" t="s">
         <v>89</v>
       </c>
       <c r="Q16" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="R16" s="12" t="s">
+      <c r="R16" s="11" t="s">
         <v>100</v>
       </c>
       <c r="S16" s="5" t="s">
@@ -3620,31 +3731,31 @@
       <c r="I17" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="J17" s="14" t="s">
+      <c r="J17" s="13" t="s">
         <v>82</v>
       </c>
       <c r="K17" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="L17" s="14" t="s">
+      <c r="L17" s="13" t="s">
         <v>82</v>
       </c>
       <c r="M17" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="N17" s="14" t="s">
+      <c r="N17" s="13" t="s">
         <v>82</v>
       </c>
       <c r="O17" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="P17" s="14" t="s">
+      <c r="P17" s="13" t="s">
         <v>89</v>
       </c>
       <c r="Q17" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="R17" s="12" t="s">
+      <c r="R17" s="11" t="s">
         <v>100</v>
       </c>
       <c r="S17" s="5" t="s">
@@ -3683,7 +3794,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="F1" s="54"/>
+      <c r="F1" s="53"/>
     </row>
     <row r="2" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -3746,7 +3857,7 @@
       <c r="T2" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="U2" s="19" t="s">
+      <c r="U2" s="18" t="s">
         <v>52</v>
       </c>
     </row>
@@ -3754,64 +3865,64 @@
       <c r="A3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>53</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="21" t="s">
         <v>53</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="21" t="s">
         <v>53</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="21" t="s">
         <v>53</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="J3" s="22" t="s">
+      <c r="J3" s="21" t="s">
         <v>53</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="L3" s="22" t="s">
+      <c r="L3" s="21" t="s">
         <v>53</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="N3" s="22" t="s">
+      <c r="N3" s="21" t="s">
         <v>53</v>
       </c>
       <c r="O3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="P3" s="22" t="s">
+      <c r="P3" s="21" t="s">
         <v>53</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="R3" s="22" t="s">
+      <c r="R3" s="21" t="s">
         <v>53</v>
       </c>
       <c r="S3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="T3" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="U3" s="19" t="s">
+      <c r="T3" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="U3" s="18" t="s">
         <v>52</v>
       </c>
     </row>
@@ -3835,48 +3946,48 @@
         <v>123</v>
       </c>
       <c r="G4" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H4" s="13">
+        <v>0.76100000000000001</v>
+      </c>
+      <c r="I4" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="H4" s="11">
-        <v>0.76100000000000001</v>
-      </c>
-      <c r="I4" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="L4" s="13">
+        <v>73</v>
+      </c>
+      <c r="M4" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="K4" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="L4" s="14">
-        <v>73</v>
-      </c>
-      <c r="M4" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="N4" s="1" t="s">
+      <c r="O4" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="P4" s="13">
+        <v>118</v>
+      </c>
+      <c r="Q4" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="R4" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="O4" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="P4" s="11">
-        <v>118</v>
-      </c>
-      <c r="Q4" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>168</v>
-      </c>
       <c r="S4" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="T4" s="14">
+      <c r="T4" s="13">
         <v>72</v>
       </c>
-      <c r="U4" s="35" t="s">
+      <c r="U4" s="34" t="s">
         <v>56</v>
       </c>
     </row>
@@ -3902,10 +4013,10 @@
       <c r="G5" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="13">
         <v>2.3199999999999998</v>
       </c>
-      <c r="I5" s="35" t="s">
+      <c r="I5" s="34" t="s">
         <v>56</v>
       </c>
       <c r="J5" s="1" t="s">
@@ -3914,22 +4025,22 @@
       <c r="K5" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="L5" s="14">
+      <c r="L5" s="13">
         <v>70</v>
       </c>
-      <c r="M5" s="35" t="s">
+      <c r="M5" s="34" t="s">
         <v>56</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>141</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="P5" s="11">
+        <v>54</v>
+      </c>
+      <c r="P5" s="13">
         <v>118</v>
       </c>
-      <c r="Q5" s="35" t="s">
+      <c r="Q5" s="34" t="s">
         <v>56</v>
       </c>
       <c r="R5" s="1" t="s">
@@ -3938,10 +4049,10 @@
       <c r="S5" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="T5" s="14">
+      <c r="T5" s="13">
         <v>72</v>
       </c>
-      <c r="U5" s="35" t="s">
+      <c r="U5" s="34" t="s">
         <v>56</v>
       </c>
     </row>
@@ -3967,34 +4078,34 @@
       <c r="G6" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="13">
         <v>3.71</v>
       </c>
-      <c r="I6" s="35" t="s">
+      <c r="I6" s="34" t="s">
         <v>56</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>151</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="L6" s="53">
+        <v>54</v>
+      </c>
+      <c r="L6" s="13">
         <v>72</v>
       </c>
-      <c r="M6" s="35" t="s">
+      <c r="M6" s="34" t="s">
         <v>56</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>142</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="P6" s="11">
+        <v>54</v>
+      </c>
+      <c r="P6" s="13">
         <v>125</v>
       </c>
-      <c r="Q6" s="35" t="s">
+      <c r="Q6" s="34" t="s">
         <v>56</v>
       </c>
       <c r="R6" s="1" t="s">
@@ -4003,10 +4114,10 @@
       <c r="S6" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="T6" s="14">
+      <c r="T6" s="13">
         <v>82</v>
       </c>
-      <c r="U6" s="35" t="s">
+      <c r="U6" s="34" t="s">
         <v>56</v>
       </c>
     </row>
@@ -4032,34 +4143,34 @@
       <c r="G7" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="13">
         <v>5.05</v>
       </c>
-      <c r="I7" s="35" t="s">
+      <c r="I7" s="34" t="s">
         <v>56</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>150</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="L7" s="53">
+        <v>54</v>
+      </c>
+      <c r="L7" s="13">
         <v>75</v>
       </c>
-      <c r="M7" s="35" t="s">
+      <c r="M7" s="34" t="s">
         <v>56</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>143</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="P7" s="11">
+        <v>54</v>
+      </c>
+      <c r="P7" s="13">
         <v>138</v>
       </c>
-      <c r="Q7" s="35" t="s">
+      <c r="Q7" s="34" t="s">
         <v>56</v>
       </c>
       <c r="R7" s="1" t="s">
@@ -4068,10 +4179,10 @@
       <c r="S7" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="T7" s="14">
+      <c r="T7" s="13">
         <v>95</v>
       </c>
-      <c r="U7" s="35" t="s">
+      <c r="U7" s="34" t="s">
         <v>56</v>
       </c>
     </row>
@@ -4097,34 +4208,34 @@
       <c r="G8" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="13">
         <v>7.1</v>
       </c>
-      <c r="I8" s="35" t="s">
+      <c r="I8" s="34" t="s">
         <v>56</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>149</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="L8" s="53">
+        <v>54</v>
+      </c>
+      <c r="L8" s="13">
         <v>76</v>
       </c>
-      <c r="M8" s="35" t="s">
+      <c r="M8" s="34" t="s">
         <v>56</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>144</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="P8" s="11">
+        <v>54</v>
+      </c>
+      <c r="P8" s="13">
         <v>140</v>
       </c>
-      <c r="Q8" s="35" t="s">
+      <c r="Q8" s="34" t="s">
         <v>56</v>
       </c>
       <c r="R8" s="1" t="s">
@@ -4133,10 +4244,10 @@
       <c r="S8" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="T8" s="14">
+      <c r="T8" s="13">
         <v>98</v>
       </c>
-      <c r="U8" s="35" t="s">
+      <c r="U8" s="34" t="s">
         <v>56</v>
       </c>
     </row>
@@ -4173,7 +4284,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="F1" s="54"/>
+      <c r="F1" s="53"/>
     </row>
     <row r="2" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -4204,13 +4315,13 @@
         <v>52</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>52</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="M2" s="5" t="s">
         <v>52</v>
@@ -4222,7 +4333,7 @@
         <v>52</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>138</v>
+        <v>184</v>
       </c>
       <c r="Q2" s="5" t="s">
         <v>52</v>
@@ -4234,9 +4345,9 @@
         <v>52</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="U2" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="U2" s="18" t="s">
         <v>52</v>
       </c>
     </row>
@@ -4244,64 +4355,64 @@
       <c r="A3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>53</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="21" t="s">
         <v>53</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="21" t="s">
         <v>53</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="21" t="s">
         <v>53</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="J3" s="22" t="s">
+      <c r="J3" s="21" t="s">
         <v>53</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="L3" s="22" t="s">
+      <c r="L3" s="21" t="s">
         <v>53</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="N3" s="22" t="s">
+      <c r="N3" s="21" t="s">
         <v>53</v>
       </c>
       <c r="O3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="P3" s="22" t="s">
+      <c r="P3" s="21" t="s">
         <v>53</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="R3" s="22" t="s">
+      <c r="R3" s="21" t="s">
         <v>53</v>
       </c>
       <c r="S3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="T3" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="U3" s="19" t="s">
+      <c r="T3" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="U3" s="18" t="s">
         <v>52</v>
       </c>
     </row>
@@ -4325,24 +4436,24 @@
         <v>129</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="H4" s="11">
+        <v>54</v>
+      </c>
+      <c r="H4" s="13">
         <v>6</v>
       </c>
-      <c r="I4" s="35" t="s">
+      <c r="I4" s="34" t="s">
         <v>56</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>161</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="L4" s="14">
+        <v>59</v>
+      </c>
+      <c r="L4" s="52">
         <v>-2</v>
       </c>
-      <c r="M4" s="35" t="s">
+      <c r="M4" s="34" t="s">
         <v>56</v>
       </c>
       <c r="N4" s="1" t="s">
@@ -4351,10 +4462,10 @@
       <c r="O4" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="P4" s="14">
+      <c r="P4" s="13">
         <v>6</v>
       </c>
-      <c r="Q4" s="35" t="s">
+      <c r="Q4" s="34" t="s">
         <v>56</v>
       </c>
       <c r="R4" s="1" t="s">
@@ -4363,10 +4474,10 @@
       <c r="S4" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="T4" s="14">
+      <c r="T4" s="13">
         <v>9</v>
       </c>
-      <c r="U4" s="35" t="s">
+      <c r="U4" s="34" t="s">
         <v>56</v>
       </c>
     </row>
@@ -4392,22 +4503,22 @@
       <c r="G5" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="13">
         <v>12.4</v>
       </c>
-      <c r="I5" s="35" t="s">
+      <c r="I5" s="34" t="s">
         <v>56</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>162</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="L5" s="11">
+        <v>59</v>
+      </c>
+      <c r="L5" s="52">
         <v>-2</v>
       </c>
-      <c r="M5" s="35" t="s">
+      <c r="M5" s="34" t="s">
         <v>56</v>
       </c>
       <c r="N5" s="1" t="s">
@@ -4416,10 +4527,10 @@
       <c r="O5" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="P5" s="14">
+      <c r="P5" s="13">
         <v>9</v>
       </c>
-      <c r="Q5" s="35" t="s">
+      <c r="Q5" s="34" t="s">
         <v>56</v>
       </c>
       <c r="R5" s="1" t="s">
@@ -4428,10 +4539,10 @@
       <c r="S5" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="T5" s="14">
+      <c r="T5" s="13">
         <v>13</v>
       </c>
-      <c r="U5" s="35" t="s">
+      <c r="U5" s="34" t="s">
         <v>56</v>
       </c>
     </row>
@@ -4457,10 +4568,10 @@
       <c r="G6" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="13">
         <v>24.9</v>
       </c>
-      <c r="I6" s="35" t="s">
+      <c r="I6" s="34" t="s">
         <v>56</v>
       </c>
       <c r="J6" s="1" t="s">
@@ -4469,22 +4580,22 @@
       <c r="K6" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="L6" s="53">
+      <c r="L6" s="52">
         <v>-1</v>
       </c>
-      <c r="M6" s="35" t="s">
+      <c r="M6" s="34" t="s">
         <v>56</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>158</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="P6" s="11">
+        <v>54</v>
+      </c>
+      <c r="P6" s="13">
         <v>13</v>
       </c>
-      <c r="Q6" s="35" t="s">
+      <c r="Q6" s="34" t="s">
         <v>56</v>
       </c>
       <c r="R6" s="1" t="s">
@@ -4493,10 +4604,10 @@
       <c r="S6" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="T6" s="14">
+      <c r="T6" s="13">
         <v>19</v>
       </c>
-      <c r="U6" s="35" t="s">
+      <c r="U6" s="34" t="s">
         <v>56</v>
       </c>
     </row>
@@ -4522,10 +4633,10 @@
       <c r="G7" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="13">
         <v>48.4</v>
       </c>
-      <c r="I7" s="35" t="s">
+      <c r="I7" s="34" t="s">
         <v>56</v>
       </c>
       <c r="J7" s="1" t="s">
@@ -4534,22 +4645,22 @@
       <c r="K7" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="L7" s="53">
+      <c r="L7" s="52">
         <v>2</v>
       </c>
-      <c r="M7" s="35" t="s">
+      <c r="M7" s="34" t="s">
         <v>56</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>157</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="P7" s="11">
+        <v>54</v>
+      </c>
+      <c r="P7" s="13">
         <v>17</v>
       </c>
-      <c r="Q7" s="35" t="s">
+      <c r="Q7" s="34" t="s">
         <v>56</v>
       </c>
       <c r="R7" s="1" t="s">
@@ -4558,15 +4669,15 @@
       <c r="S7" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="T7" s="14">
+      <c r="T7" s="13">
         <v>25</v>
       </c>
-      <c r="U7" s="35" t="s">
+      <c r="U7" s="34" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="U8" s="35"/>
+      <c r="U8" s="34"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4597,219 +4708,219 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="21"/>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
+      <c r="A1" s="20"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
     </row>
     <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" s="34" t="s">
+      <c r="A2" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="34" t="s">
+      <c r="C2" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="F2" s="26" t="s">
+      <c r="E2" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="H2" s="26" t="s">
+      <c r="G2" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H2" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="I2" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="J2" s="25" t="s">
+      <c r="I2" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="J2" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="K2" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="L2" s="17" t="s">
+      <c r="K2" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="L2" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="M2" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="N2" s="17" t="s">
+      <c r="M2" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="N2" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="O2" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="P2" s="17" t="s">
+      <c r="O2" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="P2" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="Q2" s="19" t="s">
+      <c r="Q2" s="18" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="B3" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="F3" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="H3" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="I3" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="J3" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="K3" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="L3" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="M3" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="N3" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="O3" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="P3" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q3" s="19" t="s">
+      <c r="A3" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="J3" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="K3" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="L3" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="M3" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="N3" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="O3" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="P3" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q3" s="18" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="39" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="36" t="s">
+      <c r="A4" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="C4" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="36" t="s">
+      <c r="C4" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="F4" s="36">
+      <c r="E4" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="35">
         <v>30</v>
       </c>
-      <c r="G4" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="H4" s="32">
+      <c r="G4" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H4" s="31">
         <v>450</v>
       </c>
-      <c r="I4" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="J4" s="23" t="s">
+      <c r="I4" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="J4" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="K4" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="L4" s="55" t="s">
+      <c r="K4" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="L4" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="M4" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="N4" s="23" t="s">
+      <c r="M4" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="N4" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="O4" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="P4" s="23" t="s">
+      <c r="O4" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="P4" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="Q4" s="35" t="s">
+      <c r="Q4" s="34" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="21"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="21"/>
-      <c r="N5" s="21"/>
-      <c r="O5" s="35"/>
-      <c r="P5" s="21"/>
-      <c r="Q5" s="21"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="34"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="21"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="21"/>
-      <c r="N6" s="21"/>
-      <c r="O6" s="21"/>
-      <c r="P6" s="21"/>
-      <c r="Q6" s="21"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
